--- a/data/trans_orig/P24D-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P24D-Edad-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si ha intentado alguna vez dejar de fumar en 2007</t>
+          <t>Población según si ha intentado alguna vez dejar de fumar en 2007 (tasa de respuesta: 99,45%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14249</t>
+          <t>14723</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>31794</t>
+          <t>32666</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,92%</t>
+          <t>7,15%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,43%</t>
+          <t>15,85%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>26033</t>
+          <t>25533</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>45338</t>
+          <t>45106</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>26,85%</t>
+          <t>26,71%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>44733</t>
+          <t>45048</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>71174</t>
+          <t>70774</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,93%</t>
+          <t>12,01%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>18,98%</t>
+          <t>18,88%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>174270</t>
+          <t>173398</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>191815</t>
+          <t>191341</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>84,57%</t>
+          <t>84,15%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,08%</t>
+          <t>92,85%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>123548</t>
+          <t>123780</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>142853</t>
+          <t>143353</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>73,15%</t>
+          <t>73,29%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>84,59%</t>
+          <t>84,88%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>303776</t>
+          <t>304176</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>330217</t>
+          <t>329902</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>81,02%</t>
+          <t>81,12%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,07%</t>
+          <t>87,99%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>86247</t>
+          <t>85251</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>121036</t>
+          <t>120260</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>21,62%</t>
+          <t>21,37%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>30,34%</t>
+          <t>30,14%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>66072</t>
+          <t>68628</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>94781</t>
+          <t>95844</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>28,77%</t>
+          <t>29,89%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>41,28%</t>
+          <t>41,74%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>159563</t>
+          <t>163138</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>206166</t>
+          <t>209457</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>25,38%</t>
+          <t>25,95%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>32,8%</t>
+          <t>33,32%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>277957</t>
+          <t>278733</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>312746</t>
+          <t>313742</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>69,66%</t>
+          <t>69,86%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>78,38%</t>
+          <t>78,63%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>134849</t>
+          <t>133786</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>163558</t>
+          <t>161002</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>58,72%</t>
+          <t>58,26%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>71,23%</t>
+          <t>70,11%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>422457</t>
+          <t>419166</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>469060</t>
+          <t>465485</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>67,2%</t>
+          <t>66,68%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>74,62%</t>
+          <t>74,05%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>89423</t>
+          <t>89877</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>124675</t>
+          <t>125852</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>26,3%</t>
+          <t>26,43%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>36,67%</t>
+          <t>37,01%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>97413</t>
+          <t>96972</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>129260</t>
+          <t>128744</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>38,29%</t>
+          <t>38,11%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>50,8%</t>
+          <t>50,6%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>197030</t>
+          <t>194484</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>244130</t>
+          <t>246827</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>33,15%</t>
+          <t>32,72%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>41,07%</t>
+          <t>41,52%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>215329</t>
+          <t>214152</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>250581</t>
+          <t>250127</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>63,33%</t>
+          <t>62,99%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>73,7%</t>
+          <t>73,57%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>125167</t>
+          <t>125683</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>157014</t>
+          <t>157455</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>49,2%</t>
+          <t>49,4%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>61,71%</t>
+          <t>61,89%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>350301</t>
+          <t>347604</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>397401</t>
+          <t>399947</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>58,93%</t>
+          <t>58,48%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>66,85%</t>
+          <t>67,28%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>72929</t>
+          <t>70939</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>103020</t>
+          <t>103264</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>31,21%</t>
+          <t>30,36%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>44,09%</t>
+          <t>44,19%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>40495</t>
+          <t>40796</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>64656</t>
+          <t>63743</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>28,23%</t>
+          <t>28,44%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>45,08%</t>
+          <t>44,44%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>119535</t>
+          <t>120273</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>157957</t>
+          <t>158752</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>31,7%</t>
+          <t>31,89%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>41,89%</t>
+          <t>42,1%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>130661</t>
+          <t>130417</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>160752</t>
+          <t>162742</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>55,91%</t>
+          <t>55,81%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>68,79%</t>
+          <t>69,64%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>78768</t>
+          <t>79681</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>102929</t>
+          <t>102628</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>54,92%</t>
+          <t>55,56%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>71,77%</t>
+          <t>71,56%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>219147</t>
+          <t>218352</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>257569</t>
+          <t>256831</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>58,11%</t>
+          <t>57,9%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>68,3%</t>
+          <t>68,11%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>52789</t>
+          <t>52520</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>75350</t>
+          <t>74690</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>41,33%</t>
+          <t>41,12%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>59,0%</t>
+          <t>58,48%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6406</t>
+          <t>6633</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>18229</t>
+          <t>18880</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>13,66%</t>
+          <t>14,15%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>38,88%</t>
+          <t>40,27%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>61946</t>
+          <t>62423</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>89189</t>
+          <t>89455</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>35,48%</t>
+          <t>35,75%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>51,08%</t>
+          <t>51,23%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>52365</t>
+          <t>53025</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>74926</t>
+          <t>75195</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>41,0%</t>
+          <t>41,52%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>58,67%</t>
+          <t>58,88%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>28659</t>
+          <t>28008</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>40482</t>
+          <t>40255</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>61,12%</t>
+          <t>59,73%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>86,34%</t>
+          <t>85,85%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>85414</t>
+          <t>85148</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>112657</t>
+          <t>112180</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>48,92%</t>
+          <t>48,77%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>64,52%</t>
+          <t>64,25%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>19711</t>
+          <t>19292</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>33263</t>
+          <t>32665</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>37,07%</t>
+          <t>36,28%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>62,56%</t>
+          <t>61,43%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1793</t>
+          <t>1832</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>27,23%</t>
+          <t>27,81%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>23600</t>
+          <t>23440</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>38504</t>
+          <t>38497</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>39,49%</t>
+          <t>39,22%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>64,43%</t>
+          <t>64,42%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>19910</t>
+          <t>20508</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>33462</t>
+          <t>33881</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>37,44%</t>
+          <t>38,57%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>62,93%</t>
+          <t>63,72%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2601,7 +2601,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>4792</t>
+          <t>4753</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2616,7 +2616,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>72,77%</t>
+          <t>72,19%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>21254</t>
+          <t>21261</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>36158</t>
+          <t>36318</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>35,57%</t>
+          <t>35,58%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>60,51%</t>
+          <t>60,78%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>7743</t>
+          <t>6869</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>16717</t>
+          <t>16272</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>36,52%</t>
+          <t>32,4%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>78,86%</t>
+          <t>76,75%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>8314</t>
+          <t>8057</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>18327</t>
+          <t>17807</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>32,18%</t>
+          <t>31,19%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>70,94%</t>
+          <t>68,93%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>4483</t>
+          <t>4928</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>13457</t>
+          <t>14331</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>23,25%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>63,48%</t>
+          <t>67,6%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>7507</t>
+          <t>8027</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>17520</t>
+          <t>17777</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>29,06%</t>
+          <t>31,07%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>67,82%</t>
+          <t>68,81%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>384310</t>
+          <t>387290</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>454734</t>
+          <t>456308</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>27,83%</t>
+          <t>28,05%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>32,93%</t>
+          <t>33,05%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>272592</t>
+          <t>268931</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>326520</t>
+          <t>323551</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>31,9%</t>
+          <t>31,47%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>38,21%</t>
+          <t>37,87%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>671967</t>
+          <t>671062</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>767700</t>
+          <t>759321</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>30,06%</t>
+          <t>30,02%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>34,34%</t>
+          <t>33,97%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>926094</t>
+          <t>924520</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>996518</t>
+          <t>993538</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>67,07%</t>
+          <t>66,95%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>72,17%</t>
+          <t>71,95%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>527954</t>
+          <t>530923</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>581882</t>
+          <t>585543</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>61,79%</t>
+          <t>62,13%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>68,1%</t>
+          <t>68,53%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1467602</t>
+          <t>1475981</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1563335</t>
+          <t>1564240</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>65,66%</t>
+          <t>66,03%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>69,94%</t>
+          <t>69,98%</t>
         </is>
       </c>
     </row>
@@ -3517,7 +3517,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si ha intentado alguna vez dejar de fumar en 2012</t>
+          <t>Población según si ha intentado alguna vez dejar de fumar en 2012 (tasa de respuesta: 99,63%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>45197</t>
+          <t>44296</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>68935</t>
+          <t>69514</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>27,37%</t>
+          <t>26,82%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>41,74%</t>
+          <t>42,09%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>49363</t>
+          <t>49947</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>74019</t>
+          <t>72413</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>33,72%</t>
+          <t>34,12%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>50,57%</t>
+          <t>49,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>100908</t>
+          <t>101135</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>135521</t>
+          <t>134528</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>32,39%</t>
+          <t>32,46%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>43,5%</t>
+          <t>43,18%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>96210</t>
+          <t>95631</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>119948</t>
+          <t>120849</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>58,26%</t>
+          <t>57,91%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>72,63%</t>
+          <t>73,18%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>72358</t>
+          <t>73964</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>97014</t>
+          <t>96430</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>49,43%</t>
+          <t>50,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>66,28%</t>
+          <t>65,88%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>176001</t>
+          <t>176994</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>210614</t>
+          <t>210387</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>56,5%</t>
+          <t>56,82%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>67,61%</t>
+          <t>67,54%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>124104</t>
+          <t>123988</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>161275</t>
+          <t>161306</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4070,12 +4070,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>35,67%</t>
+          <t>35,64%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>46,35%</t>
+          <t>46,36%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>123125</t>
+          <t>123716</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>155903</t>
+          <t>156747</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>49,54%</t>
+          <t>49,78%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>62,73%</t>
+          <t>63,07%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>254597</t>
+          <t>259703</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>307015</t>
+          <t>308530</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>42,69%</t>
+          <t>43,54%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>51,47%</t>
+          <t>51,73%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>186638</t>
+          <t>186607</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>223809</t>
+          <t>223925</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,12 +4183,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>53,65%</t>
+          <t>53,64%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>64,33%</t>
+          <t>64,36%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>92631</t>
+          <t>91787</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>125409</t>
+          <t>124818</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>37,27%</t>
+          <t>36,93%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>50,46%</t>
+          <t>50,22%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>289432</t>
+          <t>287917</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>341850</t>
+          <t>336744</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>48,53%</t>
+          <t>48,27%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>57,31%</t>
+          <t>56,46%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>139775</t>
+          <t>140439</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>176606</t>
+          <t>176232</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>43,09%</t>
+          <t>43,29%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>54,44%</t>
+          <t>54,33%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>112582</t>
+          <t>111431</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>143572</t>
+          <t>143415</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>45,35%</t>
+          <t>44,89%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>57,84%</t>
+          <t>57,77%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>260999</t>
+          <t>261967</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>310998</t>
+          <t>309460</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>45,58%</t>
+          <t>45,75%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>54,31%</t>
+          <t>54,04%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>147771</t>
+          <t>148145</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>184602</t>
+          <t>183938</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>45,56%</t>
+          <t>45,67%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>56,91%</t>
+          <t>56,71%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>104667</t>
+          <t>104824</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>135657</t>
+          <t>136808</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>42,16%</t>
+          <t>42,23%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>54,65%</t>
+          <t>55,11%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>261618</t>
+          <t>263156</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>311617</t>
+          <t>310649</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>45,69%</t>
+          <t>45,96%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>54,42%</t>
+          <t>54,25%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>128705</t>
+          <t>126099</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>164060</t>
+          <t>162504</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>46,0%</t>
+          <t>45,07%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>58,64%</t>
+          <t>58,08%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>114110</t>
+          <t>114381</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>147454</t>
+          <t>147539</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>48,13%</t>
+          <t>48,24%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>62,19%</t>
+          <t>62,23%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>254684</t>
+          <t>252854</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>303169</t>
+          <t>301045</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>49,27%</t>
+          <t>48,92%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>58,65%</t>
+          <t>58,24%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>115722</t>
+          <t>117278</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>151077</t>
+          <t>153683</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>41,36%</t>
+          <t>41,92%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>54,0%</t>
+          <t>54,93%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>89639</t>
+          <t>89554</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>122983</t>
+          <t>122712</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>37,81%</t>
+          <t>37,77%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>51,87%</t>
+          <t>51,76%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>213706</t>
+          <t>215830</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>262191</t>
+          <t>264021</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>41,35%</t>
+          <t>41,76%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>50,73%</t>
+          <t>51,08%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>73655</t>
+          <t>73938</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>99567</t>
+          <t>99627</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>47,1%</t>
+          <t>47,28%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>63,67%</t>
+          <t>63,71%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>17833</t>
+          <t>18016</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>35291</t>
+          <t>35090</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>27,05%</t>
+          <t>27,33%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>53,54%</t>
+          <t>53,23%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>96084</t>
+          <t>96753</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>127770</t>
+          <t>128099</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>43,22%</t>
+          <t>43,53%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>57,48%</t>
+          <t>57,63%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>56802</t>
+          <t>56742</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>82714</t>
+          <t>82431</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>36,33%</t>
+          <t>36,29%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>52,9%</t>
+          <t>52,72%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>30629</t>
+          <t>30830</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>48087</t>
+          <t>47904</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>46,46%</t>
+          <t>46,77%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>72,95%</t>
+          <t>72,67%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>94519</t>
+          <t>94190</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>126205</t>
+          <t>125536</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>42,52%</t>
+          <t>42,37%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>56,78%</t>
+          <t>56,47%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>17837</t>
+          <t>17559</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>33702</t>
+          <t>33028</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>34,8%</t>
+          <t>34,26%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>65,76%</t>
+          <t>64,44%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>3164</t>
+          <t>2925</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>12467</t>
+          <t>12175</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>16,65%</t>
+          <t>15,39%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>65,6%</t>
+          <t>64,07%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>22805</t>
+          <t>24029</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>40877</t>
+          <t>41931</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>32,46%</t>
+          <t>34,2%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>58,18%</t>
+          <t>59,68%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>17552</t>
+          <t>18226</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>33417</t>
+          <t>33695</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>34,24%</t>
+          <t>35,56%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>65,2%</t>
+          <t>65,74%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>6536</t>
+          <t>6828</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>15839</t>
+          <t>16078</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>34,4%</t>
+          <t>35,93%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>83,35%</t>
+          <t>84,61%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>29380</t>
+          <t>28326</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>47452</t>
+          <t>46228</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>41,82%</t>
+          <t>40,32%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>67,54%</t>
+          <t>65,8%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>7785</t>
+          <t>7388</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>18917</t>
+          <t>18487</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>28,78%</t>
+          <t>27,31%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>69,93%</t>
+          <t>68,34%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>8604</t>
+          <t>8687</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>19782</t>
+          <t>20497</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>27,68%</t>
+          <t>27,95%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>63,65%</t>
+          <t>65,95%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>8135</t>
+          <t>8565</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>19267</t>
+          <t>19664</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>30,07%</t>
+          <t>31,66%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>71,22%</t>
+          <t>72,69%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>11298</t>
+          <t>10583</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>22476</t>
+          <t>22393</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>36,35%</t>
+          <t>34,05%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>72,32%</t>
+          <t>72,05%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>590891</t>
+          <t>588595</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>663949</t>
+          <t>664147</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>43,71%</t>
+          <t>43,54%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>49,11%</t>
+          <t>49,13%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>467390</t>
+          <t>463910</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>530327</t>
+          <t>527689</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>48,22%</t>
+          <t>47,87%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>54,72%</t>
+          <t>54,45%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1066822</t>
+          <t>1075336</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1170387</t>
+          <t>1178002</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>45,96%</t>
+          <t>46,33%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>50,42%</t>
+          <t>50,75%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>687943</t>
+          <t>687745</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>761001</t>
+          <t>763297</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>50,89%</t>
+          <t>50,87%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>56,29%</t>
+          <t>56,46%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>438867</t>
+          <t>441505</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>501804</t>
+          <t>505284</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>45,28%</t>
+          <t>45,55%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>51,78%</t>
+          <t>52,13%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1150699</t>
+          <t>1143084</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1254264</t>
+          <t>1245750</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>49,58%</t>
+          <t>49,25%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>54,04%</t>
+          <t>53,67%</t>
         </is>
       </c>
     </row>
@@ -6496,7 +6496,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si ha intentado alguna vez dejar de fumar en 2016</t>
+          <t>Población según si ha intentado alguna vez dejar de fumar en 2016 (tasa de respuesta: 99,25%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6691,12 +6691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>29239</t>
+          <t>28861</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>51389</t>
+          <t>51496</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>20,55%</t>
+          <t>20,28%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>36,11%</t>
+          <t>36,19%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>25929</t>
+          <t>25960</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>44798</t>
+          <t>44785</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>24,59%</t>
+          <t>24,62%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>42,48%</t>
+          <t>42,47%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>59497</t>
+          <t>61079</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>88737</t>
+          <t>88851</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>24,01%</t>
+          <t>24,65%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>35,82%</t>
+          <t>35,86%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>90913</t>
+          <t>90806</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>113063</t>
+          <t>113441</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>63,89%</t>
+          <t>63,81%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>79,45%</t>
+          <t>79,72%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>60649</t>
+          <t>60662</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>79518</t>
+          <t>79487</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>57,52%</t>
+          <t>57,53%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>75,41%</t>
+          <t>75,38%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>159011</t>
+          <t>158897</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>188251</t>
+          <t>186669</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>64,18%</t>
+          <t>64,14%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>75,99%</t>
+          <t>75,35%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>82628</t>
+          <t>83364</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>115037</t>
+          <t>116309</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>31,65%</t>
+          <t>31,93%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>44,06%</t>
+          <t>44,55%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>74693</t>
+          <t>74202</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>102689</t>
+          <t>102118</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>35,06%</t>
+          <t>34,83%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>48,2%</t>
+          <t>47,94%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>163664</t>
+          <t>167494</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>207478</t>
+          <t>208490</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>34,52%</t>
+          <t>35,33%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>43,76%</t>
+          <t>43,97%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>146045</t>
+          <t>144773</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>178454</t>
+          <t>177718</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>55,94%</t>
+          <t>55,45%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>68,35%</t>
+          <t>68,07%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>110342</t>
+          <t>110913</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>138338</t>
+          <t>138829</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>51,8%</t>
+          <t>52,06%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>64,94%</t>
+          <t>65,17%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>266635</t>
+          <t>265623</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>310449</t>
+          <t>306619</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>56,24%</t>
+          <t>56,03%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>65,48%</t>
+          <t>64,67%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>108891</t>
+          <t>107977</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>144069</t>
+          <t>141533</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>40,93%</t>
+          <t>40,59%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>54,16%</t>
+          <t>53,2%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>77409</t>
+          <t>78804</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>106618</t>
+          <t>105153</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>35,1%</t>
+          <t>35,73%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>48,34%</t>
+          <t>47,68%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>193864</t>
+          <t>197260</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>239856</t>
+          <t>239961</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>39,84%</t>
+          <t>40,54%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>49,3%</t>
+          <t>49,32%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>121954</t>
+          <t>124490</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>157132</t>
+          <t>158046</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>45,84%</t>
+          <t>46,8%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>59,07%</t>
+          <t>59,41%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>113926</t>
+          <t>115391</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>143135</t>
+          <t>141740</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>51,66%</t>
+          <t>52,32%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>64,9%</t>
+          <t>64,27%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>246711</t>
+          <t>246606</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>292703</t>
+          <t>289307</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>50,7%</t>
+          <t>50,68%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>60,16%</t>
+          <t>59,46%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>100368</t>
+          <t>101005</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>136160</t>
+          <t>134608</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>36,13%</t>
+          <t>36,36%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>49,01%</t>
+          <t>48,46%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>102177</t>
+          <t>101310</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>134949</t>
+          <t>133309</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>44,27%</t>
+          <t>43,89%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>58,46%</t>
+          <t>57,75%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>212824</t>
+          <t>214687</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>259656</t>
+          <t>260641</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>41,84%</t>
+          <t>42,21%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>51,05%</t>
+          <t>51,24%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>141638</t>
+          <t>143190</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>177430</t>
+          <t>176793</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>50,99%</t>
+          <t>51,54%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>63,87%</t>
+          <t>63,64%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>95880</t>
+          <t>97520</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>128652</t>
+          <t>129519</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>41,54%</t>
+          <t>42,25%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>55,73%</t>
+          <t>56,11%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>248971</t>
+          <t>247986</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>295803</t>
+          <t>293940</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>48,95%</t>
+          <t>48,76%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>58,16%</t>
+          <t>57,79%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>69110</t>
+          <t>68454</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>93067</t>
+          <t>92859</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,12 +8078,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>47,07%</t>
+          <t>46,62%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>63,38%</t>
+          <t>63,24%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>44069</t>
+          <t>44490</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>67224</t>
+          <t>68460</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>38,63%</t>
+          <t>39,0%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>58,92%</t>
+          <t>60,01%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>119996</t>
+          <t>121414</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>155040</t>
+          <t>155337</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>45,99%</t>
+          <t>46,53%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>59,42%</t>
+          <t>59,53%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>53769</t>
+          <t>53977</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>77726</t>
+          <t>78382</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8191,12 +8191,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>36,62%</t>
+          <t>36,76%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>52,93%</t>
+          <t>53,38%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>46863</t>
+          <t>45627</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>70018</t>
+          <t>69597</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>41,08%</t>
+          <t>39,99%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>61,37%</t>
+          <t>61,0%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>105884</t>
+          <t>105587</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>140928</t>
+          <t>139510</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>40,58%</t>
+          <t>40,47%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>54,01%</t>
+          <t>53,47%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>20876</t>
+          <t>21434</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>36829</t>
+          <t>36775</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>35,85%</t>
+          <t>36,81%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>63,25%</t>
+          <t>63,15%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8253</t>
+          <t>8626</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>19898</t>
+          <t>19991</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>27,49%</t>
+          <t>28,73%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>66,27%</t>
+          <t>66,58%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>33412</t>
+          <t>33743</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>52752</t>
+          <t>52984</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>37,86%</t>
+          <t>38,23%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>59,77%</t>
+          <t>60,03%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>21403</t>
+          <t>21457</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>37356</t>
+          <t>36798</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>36,75%</t>
+          <t>36,85%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>64,15%</t>
+          <t>63,19%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>10129</t>
+          <t>10036</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>21774</t>
+          <t>21401</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>33,73%</t>
+          <t>33,42%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>72,51%</t>
+          <t>71,27%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>35507</t>
+          <t>35275</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>54847</t>
+          <t>54516</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>40,23%</t>
+          <t>39,97%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>62,14%</t>
+          <t>61,77%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>8273</t>
+          <t>8188</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>16645</t>
+          <t>16558</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>34,67%</t>
+          <t>34,31%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>69,75%</t>
+          <t>69,39%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,7 +8784,7 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>1491</t>
+          <t>2790</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
@@ -8799,7 +8799,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>18,6%</t>
+          <t>34,81%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>12077</t>
+          <t>12544</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>22806</t>
+          <t>23628</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>37,89%</t>
+          <t>39,35%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>71,54%</t>
+          <t>74,12%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>7218</t>
+          <t>7305</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>15590</t>
+          <t>15675</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>30,25%</t>
+          <t>30,61%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>65,33%</t>
+          <t>65,69%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8902,7 +8902,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>6523</t>
+          <t>5224</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8917,7 +8917,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>81,4%</t>
+          <t>65,19%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>9071</t>
+          <t>8249</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>19800</t>
+          <t>19333</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>28,46%</t>
+          <t>25,88%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>62,11%</t>
+          <t>60,65%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>467578</t>
+          <t>470680</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>534850</t>
+          <t>539975</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9107,12 +9107,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>39,76%</t>
+          <t>40,02%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>45,48%</t>
+          <t>45,91%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>377594</t>
+          <t>379914</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>439527</t>
+          <t>442177</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>40,95%</t>
+          <t>41,21%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>47,67%</t>
+          <t>47,96%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>868127</t>
+          <t>868049</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>960933</t>
+          <t>964351</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>41,38%</t>
+          <t>41,37%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>45,8%</t>
+          <t>45,96%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>641287</t>
+          <t>636162</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>708559</t>
+          <t>705457</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,12 +9220,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>54,52%</t>
+          <t>54,09%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>60,24%</t>
+          <t>59,98%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>482452</t>
+          <t>479802</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>544385</t>
+          <t>542065</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>52,33%</t>
+          <t>52,04%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>59,05%</t>
+          <t>58,79%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1137183</t>
+          <t>1133765</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1229989</t>
+          <t>1230067</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>54,2%</t>
+          <t>54,04%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>58,62%</t>
+          <t>58,63%</t>
         </is>
       </c>
     </row>
@@ -9475,7 +9475,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según si ha intentado alguna vez dejar de fumar en 2023</t>
+          <t>Población según si ha intentado alguna vez dejar de fumar en 2023 (tasa de respuesta: 99,32%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -9670,12 +9670,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5841</t>
+          <t>5008</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>30202</t>
+          <t>27706</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -9685,12 +9685,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>6,68%</t>
+          <t>5,72%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>34,51%</t>
+          <t>31,66%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9705,12 +9705,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>6561</t>
+          <t>7705</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>26691</t>
+          <t>26918</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -9720,12 +9720,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,64%</t>
+          <t>12,49%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>43,28%</t>
+          <t>43,65%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9740,12 +9740,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>17180</t>
+          <t>16628</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>49597</t>
+          <t>47298</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -9755,12 +9755,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,15%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>33,25%</t>
+          <t>31,7%</t>
         </is>
       </c>
     </row>
@@ -9783,12 +9783,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>57307</t>
+          <t>59803</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>81668</t>
+          <t>82501</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -9798,12 +9798,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>65,49%</t>
+          <t>68,34%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>93,32%</t>
+          <t>94,28%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9818,12 +9818,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>34983</t>
+          <t>34756</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>55113</t>
+          <t>53969</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -9833,12 +9833,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>56,72%</t>
+          <t>56,35%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,36%</t>
+          <t>87,51%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9853,12 +9853,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>99586</t>
+          <t>101885</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>132003</t>
+          <t>132555</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -9868,12 +9868,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>66,75%</t>
+          <t>68,3%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,48%</t>
+          <t>88,85%</t>
         </is>
       </c>
     </row>
@@ -10013,12 +10013,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>22425</t>
+          <t>23998</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>49489</t>
+          <t>50222</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -10028,12 +10028,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>16,32%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>33,66%</t>
+          <t>34,16%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10048,12 +10048,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>31948</t>
+          <t>32490</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>53252</t>
+          <t>53428</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -10063,12 +10063,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>28,09%</t>
+          <t>28,56%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>46,82%</t>
+          <t>46,97%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10083,12 +10083,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>59543</t>
+          <t>60285</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>96096</t>
+          <t>95043</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -10098,12 +10098,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>23,12%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>36,85%</t>
+          <t>36,45%</t>
         </is>
       </c>
     </row>
@@ -10126,12 +10126,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>97540</t>
+          <t>96807</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>124604</t>
+          <t>123031</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -10141,12 +10141,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>66,34%</t>
+          <t>65,84%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>84,75%</t>
+          <t>83,68%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10161,12 +10161,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>60497</t>
+          <t>60321</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>81801</t>
+          <t>81259</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -10176,12 +10176,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>53,18%</t>
+          <t>53,03%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>71,91%</t>
+          <t>71,44%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10196,12 +10196,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>164681</t>
+          <t>165734</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>201234</t>
+          <t>200492</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -10211,12 +10211,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>63,15%</t>
+          <t>63,55%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>77,17%</t>
+          <t>76,88%</t>
         </is>
       </c>
     </row>
@@ -10356,12 +10356,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>41426</t>
+          <t>40889</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>66303</t>
+          <t>65878</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -10371,12 +10371,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>27,68%</t>
+          <t>27,32%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>44,31%</t>
+          <t>44,02%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10391,12 +10391,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>52466</t>
+          <t>52389</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>71342</t>
+          <t>71636</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -10406,12 +10406,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>38,89%</t>
+          <t>38,83%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>52,88%</t>
+          <t>53,09%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10426,12 +10426,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>100451</t>
+          <t>99392</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>130728</t>
+          <t>129385</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -10441,12 +10441,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>35,3%</t>
+          <t>34,93%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>45,94%</t>
+          <t>45,47%</t>
         </is>
       </c>
     </row>
@@ -10469,12 +10469,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>83344</t>
+          <t>83769</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>108221</t>
+          <t>108758</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -10484,12 +10484,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>55,69%</t>
+          <t>55,98%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>72,32%</t>
+          <t>72,68%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10504,12 +10504,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>63580</t>
+          <t>63286</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>82456</t>
+          <t>82533</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -10519,12 +10519,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>47,12%</t>
+          <t>46,91%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>61,11%</t>
+          <t>61,17%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10539,12 +10539,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>153841</t>
+          <t>155184</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>184118</t>
+          <t>185177</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -10554,12 +10554,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>54,06%</t>
+          <t>54,53%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>64,7%</t>
+          <t>65,07%</t>
         </is>
       </c>
     </row>
@@ -10699,12 +10699,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>61603</t>
+          <t>63006</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>96058</t>
+          <t>97496</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -10714,12 +10714,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>33,34%</t>
+          <t>34,1%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>51,99%</t>
+          <t>52,77%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -10734,12 +10734,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>68543</t>
+          <t>68259</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>87554</t>
+          <t>86949</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -10749,12 +10749,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>42,51%</t>
+          <t>42,34%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>54,3%</t>
+          <t>53,93%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10769,12 +10769,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>137164</t>
+          <t>138246</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>174017</t>
+          <t>175241</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -10784,12 +10784,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>39,64%</t>
+          <t>39,96%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>50,29%</t>
+          <t>50,65%</t>
         </is>
       </c>
     </row>
@@ -10812,12 +10812,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>88700</t>
+          <t>87262</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>123155</t>
+          <t>121752</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -10827,12 +10827,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>48,01%</t>
+          <t>47,23%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>66,66%</t>
+          <t>65,9%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -10847,12 +10847,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>73680</t>
+          <t>74285</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>92691</t>
+          <t>92975</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -10862,12 +10862,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>45,7%</t>
+          <t>46,07%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>57,49%</t>
+          <t>57,66%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -10882,12 +10882,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>171975</t>
+          <t>170751</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>208828</t>
+          <t>207746</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -10897,12 +10897,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>49,71%</t>
+          <t>49,35%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>60,36%</t>
+          <t>60,04%</t>
         </is>
       </c>
     </row>
@@ -11042,12 +11042,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>59178</t>
+          <t>59373</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>84652</t>
+          <t>83559</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -11057,12 +11057,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>34,56%</t>
+          <t>34,67%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>49,44%</t>
+          <t>48,8%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11077,12 +11077,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>52227</t>
+          <t>52795</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>67983</t>
+          <t>68860</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -11092,12 +11092,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>43,61%</t>
+          <t>44,09%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>56,77%</t>
+          <t>57,5%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11112,12 +11112,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>117326</t>
+          <t>116950</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>148568</t>
+          <t>146997</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -11127,12 +11127,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>40,32%</t>
+          <t>40,19%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>51,06%</t>
+          <t>50,52%</t>
         </is>
       </c>
     </row>
@@ -11155,12 +11155,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>86587</t>
+          <t>87680</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>112061</t>
+          <t>111866</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -11170,12 +11170,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>50,56%</t>
+          <t>51,2%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>65,44%</t>
+          <t>65,33%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11190,12 +11190,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>51770</t>
+          <t>50893</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>67526</t>
+          <t>66958</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -11205,12 +11205,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>43,23%</t>
+          <t>42,5%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>56,39%</t>
+          <t>55,91%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11225,12 +11225,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>142424</t>
+          <t>143995</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>173666</t>
+          <t>174042</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -11240,12 +11240,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>48,94%</t>
+          <t>49,48%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>59,68%</t>
+          <t>59,81%</t>
         </is>
       </c>
     </row>
@@ -11385,12 +11385,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>26294</t>
+          <t>26353</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>39302</t>
+          <t>39849</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -11400,12 +11400,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>38,9%</t>
+          <t>38,99%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>58,14%</t>
+          <t>58,95%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11420,12 +11420,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>16950</t>
+          <t>16565</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>26592</t>
+          <t>26960</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -11435,12 +11435,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>34,75%</t>
+          <t>33,96%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>54,51%</t>
+          <t>55,27%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11455,12 +11455,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>46483</t>
+          <t>46389</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>62535</t>
+          <t>63151</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -11470,12 +11470,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>39,94%</t>
+          <t>39,86%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>53,74%</t>
+          <t>54,27%</t>
         </is>
       </c>
     </row>
@@ -11498,12 +11498,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>28293</t>
+          <t>27746</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>41301</t>
+          <t>41242</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -11513,12 +11513,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>41,86%</t>
+          <t>41,05%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>61,1%</t>
+          <t>61,01%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11533,12 +11533,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>22188</t>
+          <t>21820</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>31830</t>
+          <t>32215</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -11548,12 +11548,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>45,49%</t>
+          <t>44,73%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>65,25%</t>
+          <t>66,04%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11568,12 +11568,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>53839</t>
+          <t>53223</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>69891</t>
+          <t>69985</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -11583,12 +11583,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>46,26%</t>
+          <t>45,73%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>60,06%</t>
+          <t>60,14%</t>
         </is>
       </c>
     </row>
@@ -11728,12 +11728,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3238</t>
+          <t>3063</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>9117</t>
+          <t>9495</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -11743,12 +11743,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>16,09%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>47,91%</t>
+          <t>49,89%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11763,12 +11763,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>601</t>
+          <t>585</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>4204</t>
+          <t>4139</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -11778,12 +11778,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>9,56%</t>
+          <t>9,3%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>66,79%</t>
+          <t>65,76%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11798,12 +11798,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>4936</t>
+          <t>5141</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>12116</t>
+          <t>11924</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -11813,12 +11813,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>19,49%</t>
+          <t>20,3%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>47,84%</t>
+          <t>47,09%</t>
         </is>
       </c>
     </row>
@@ -11841,12 +11841,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>9914</t>
+          <t>9536</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>15793</t>
+          <t>15968</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -11856,12 +11856,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>52,09%</t>
+          <t>50,11%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>82,99%</t>
+          <t>83,91%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11876,12 +11876,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2090</t>
+          <t>2155</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>5693</t>
+          <t>5709</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -11891,12 +11891,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>33,21%</t>
+          <t>34,24%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>90,44%</t>
+          <t>90,7%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11911,12 +11911,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>13209</t>
+          <t>13401</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>20389</t>
+          <t>20184</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -11926,12 +11926,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>52,16%</t>
+          <t>52,91%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>80,51%</t>
+          <t>79,7%</t>
         </is>
       </c>
     </row>
@@ -12071,12 +12071,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>261761</t>
+          <t>263266</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>325962</t>
+          <t>325930</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -12086,7 +12086,7 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>31,66%</t>
+          <t>31,84%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
@@ -12106,12 +12106,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>261133</t>
+          <t>259098</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>305334</t>
+          <t>304949</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -12121,12 +12121,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>40,4%</t>
+          <t>40,08%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>47,24%</t>
+          <t>47,18%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12141,12 +12141,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>534770</t>
+          <t>533230</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>616261</t>
+          <t>613310</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -12156,12 +12156,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>36,3%</t>
+          <t>36,2%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>41,83%</t>
+          <t>41,63%</t>
         </is>
       </c>
     </row>
@@ -12184,12 +12184,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>500846</t>
+          <t>500878</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>565047</t>
+          <t>563542</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -12204,7 +12204,7 @@
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>68,34%</t>
+          <t>68,16%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12219,12 +12219,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>341071</t>
+          <t>341456</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>385272</t>
+          <t>387307</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -12234,12 +12234,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>52,76%</t>
+          <t>52,82%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>59,6%</t>
+          <t>59,92%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12254,12 +12254,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>856951</t>
+          <t>859902</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>938442</t>
+          <t>939982</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -12269,12 +12269,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>58,17%</t>
+          <t>58,37%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>63,7%</t>
+          <t>63,8%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P24D-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P24D-Edad-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>14723</t>
+          <t>15040</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>32666</t>
+          <t>31828</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>7,3%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>15,85%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>25533</t>
+          <t>24618</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>45106</t>
+          <t>45131</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>14,58%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>26,71%</t>
+          <t>26,72%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>45048</t>
+          <t>44901</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>70774</t>
+          <t>71480</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,01%</t>
+          <t>11,98%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>18,88%</t>
+          <t>19,06%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>173398</t>
+          <t>174236</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>191341</t>
+          <t>191024</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>84,15%</t>
+          <t>84,55%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>92,85%</t>
+          <t>92,7%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>123780</t>
+          <t>123755</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>143353</t>
+          <t>144268</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>73,29%</t>
+          <t>73,28%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>84,88%</t>
+          <t>85,42%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>304176</t>
+          <t>303470</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>329902</t>
+          <t>330049</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>81,12%</t>
+          <t>80,94%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>87,99%</t>
+          <t>88,02%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>85251</t>
+          <t>85532</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>120260</t>
+          <t>121580</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>21,37%</t>
+          <t>21,44%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>30,14%</t>
+          <t>30,47%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>68628</t>
+          <t>66021</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>95844</t>
+          <t>96120</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>29,89%</t>
+          <t>28,75%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>41,74%</t>
+          <t>41,86%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>163138</t>
+          <t>161051</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>209457</t>
+          <t>206913</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>25,95%</t>
+          <t>25,62%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>33,32%</t>
+          <t>32,92%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>278733</t>
+          <t>277413</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>313742</t>
+          <t>313461</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>69,86%</t>
+          <t>69,53%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>78,63%</t>
+          <t>78,56%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>133786</t>
+          <t>133510</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>161002</t>
+          <t>163609</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>58,26%</t>
+          <t>58,14%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>70,11%</t>
+          <t>71,25%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>419166</t>
+          <t>421710</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>465485</t>
+          <t>467572</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>66,68%</t>
+          <t>67,08%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>74,05%</t>
+          <t>74,38%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>89877</t>
+          <t>89686</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>125852</t>
+          <t>123445</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>26,43%</t>
+          <t>26,38%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>37,01%</t>
+          <t>36,31%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>96972</t>
+          <t>95975</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>128744</t>
+          <t>128297</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>38,11%</t>
+          <t>37,72%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>50,6%</t>
+          <t>50,43%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>194484</t>
+          <t>196260</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>246827</t>
+          <t>243930</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>32,72%</t>
+          <t>33,02%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>41,52%</t>
+          <t>41,04%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>214152</t>
+          <t>216559</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>250127</t>
+          <t>250318</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>62,99%</t>
+          <t>63,69%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>73,57%</t>
+          <t>73,62%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>125683</t>
+          <t>126130</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>157455</t>
+          <t>158452</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>49,4%</t>
+          <t>49,57%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>61,89%</t>
+          <t>62,28%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>347604</t>
+          <t>350501</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>399947</t>
+          <t>398171</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>58,48%</t>
+          <t>58,96%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>67,28%</t>
+          <t>66,98%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>70939</t>
+          <t>70524</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>103264</t>
+          <t>102082</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>30,36%</t>
+          <t>30,18%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>44,19%</t>
+          <t>43,68%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>40796</t>
+          <t>41204</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>63743</t>
+          <t>64671</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>28,44%</t>
+          <t>28,73%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>44,44%</t>
+          <t>45,09%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>120273</t>
+          <t>120075</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>158752</t>
+          <t>159057</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>31,89%</t>
+          <t>31,84%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>42,1%</t>
+          <t>42,18%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>130417</t>
+          <t>131599</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>162742</t>
+          <t>163157</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>55,81%</t>
+          <t>56,32%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>69,64%</t>
+          <t>69,82%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>79681</t>
+          <t>78753</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>102628</t>
+          <t>102220</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>55,56%</t>
+          <t>54,91%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>71,56%</t>
+          <t>71,27%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>218352</t>
+          <t>218047</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>256831</t>
+          <t>257029</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>57,9%</t>
+          <t>57,82%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>68,11%</t>
+          <t>68,16%</t>
         </is>
       </c>
     </row>
@@ -2105,12 +2105,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>52520</t>
+          <t>51850</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>74690</t>
+          <t>74289</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2120,12 +2120,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>41,12%</t>
+          <t>40,6%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>58,48%</t>
+          <t>58,17%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2140,12 +2140,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>6633</t>
+          <t>7114</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>18880</t>
+          <t>19250</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2155,12 +2155,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>14,15%</t>
+          <t>15,17%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>40,27%</t>
+          <t>41,06%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2175,12 +2175,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>62423</t>
+          <t>62642</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>89455</t>
+          <t>88615</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2190,12 +2190,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>35,75%</t>
+          <t>35,88%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>51,23%</t>
+          <t>50,75%</t>
         </is>
       </c>
     </row>
@@ -2218,12 +2218,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>53025</t>
+          <t>53426</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>75195</t>
+          <t>75865</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2233,12 +2233,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>41,52%</t>
+          <t>41,83%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>58,88%</t>
+          <t>59,4%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2253,12 +2253,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>28008</t>
+          <t>27638</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>40255</t>
+          <t>39774</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2268,12 +2268,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>59,73%</t>
+          <t>58,94%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>85,85%</t>
+          <t>84,83%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2288,12 +2288,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>85148</t>
+          <t>85988</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>112180</t>
+          <t>111961</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2303,12 +2303,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>48,77%</t>
+          <t>49,25%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>64,25%</t>
+          <t>64,12%</t>
         </is>
       </c>
     </row>
@@ -2448,12 +2448,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>19292</t>
+          <t>19716</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>32665</t>
+          <t>32803</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2463,12 +2463,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>36,28%</t>
+          <t>37,08%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>61,43%</t>
+          <t>61,69%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2483,7 +2483,7 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>1832</t>
+          <t>1793</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
@@ -2498,7 +2498,7 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>27,81%</t>
+          <t>27,23%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
@@ -2518,12 +2518,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>23440</t>
+          <t>23764</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>38497</t>
+          <t>37725</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2533,12 +2533,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>39,22%</t>
+          <t>39,77%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>64,42%</t>
+          <t>63,13%</t>
         </is>
       </c>
     </row>
@@ -2561,12 +2561,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>20508</t>
+          <t>20370</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>33881</t>
+          <t>33457</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2576,12 +2576,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>38,57%</t>
+          <t>38,31%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>63,72%</t>
+          <t>62,92%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2601,7 +2601,7 @@
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>4753</t>
+          <t>4792</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2616,7 +2616,7 @@
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>72,19%</t>
+          <t>72,77%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2631,12 +2631,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>21261</t>
+          <t>22033</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>36318</t>
+          <t>35994</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2646,12 +2646,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>35,58%</t>
+          <t>36,87%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>60,78%</t>
+          <t>60,23%</t>
         </is>
       </c>
     </row>
@@ -2791,12 +2791,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>6869</t>
+          <t>7765</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>16272</t>
+          <t>16426</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2806,12 +2806,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>32,4%</t>
+          <t>36,63%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>76,75%</t>
+          <t>77,48%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2831,7 +2831,7 @@
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>3442</t>
+          <t>4635</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2846,7 +2846,7 @@
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>74,26%</t>
+          <t>100,0%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2861,12 +2861,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>8057</t>
+          <t>8014</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>17807</t>
+          <t>18160</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2876,12 +2876,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>31,19%</t>
+          <t>31,02%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>68,93%</t>
+          <t>70,29%</t>
         </is>
       </c>
     </row>
@@ -2904,12 +2904,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>4928</t>
+          <t>4774</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>14331</t>
+          <t>13435</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2919,12 +2919,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>23,25%</t>
+          <t>22,52%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>67,6%</t>
+          <t>63,37%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2939,7 +2939,7 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>1193</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>25,74%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
@@ -2974,12 +2974,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>8027</t>
+          <t>7674</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>17777</t>
+          <t>17820</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2989,12 +2989,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>31,07%</t>
+          <t>29,71%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>68,81%</t>
+          <t>68,98%</t>
         </is>
       </c>
     </row>
@@ -3134,12 +3134,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>387290</t>
+          <t>387022</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>456308</t>
+          <t>457836</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3149,12 +3149,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>28,05%</t>
+          <t>28,03%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>33,05%</t>
+          <t>33,16%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3169,12 +3169,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>268931</t>
+          <t>268296</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>323551</t>
+          <t>324646</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3184,12 +3184,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>31,47%</t>
+          <t>31,4%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>37,87%</t>
+          <t>37,99%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3204,12 +3204,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>671062</t>
+          <t>673899</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>759321</t>
+          <t>762196</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3219,12 +3219,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>30,02%</t>
+          <t>30,15%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>33,97%</t>
+          <t>34,1%</t>
         </is>
       </c>
     </row>
@@ -3247,12 +3247,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>924520</t>
+          <t>922992</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>993538</t>
+          <t>993806</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3262,12 +3262,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>66,95%</t>
+          <t>66,84%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>71,95%</t>
+          <t>71,97%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3282,12 +3282,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>530923</t>
+          <t>529828</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>585543</t>
+          <t>586178</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3297,12 +3297,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>62,13%</t>
+          <t>62,01%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>68,53%</t>
+          <t>68,6%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3317,12 +3317,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1475981</t>
+          <t>1473106</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1564240</t>
+          <t>1561403</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3332,12 +3332,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>66,03%</t>
+          <t>65,9%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>69,98%</t>
+          <t>69,85%</t>
         </is>
       </c>
     </row>
@@ -3712,12 +3712,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>44296</t>
+          <t>44445</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>69514</t>
+          <t>68395</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3727,12 +3727,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>26,82%</t>
+          <t>26,91%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>42,09%</t>
+          <t>41,42%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3747,12 +3747,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>49947</t>
+          <t>50049</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>72413</t>
+          <t>74065</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3762,12 +3762,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>34,12%</t>
+          <t>34,19%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>49,47%</t>
+          <t>50,6%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3782,12 +3782,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>101135</t>
+          <t>102397</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>134528</t>
+          <t>135755</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3797,12 +3797,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>32,46%</t>
+          <t>32,87%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>43,18%</t>
+          <t>43,58%</t>
         </is>
       </c>
     </row>
@@ -3825,12 +3825,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>95631</t>
+          <t>96750</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>120849</t>
+          <t>120700</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3840,12 +3840,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>57,91%</t>
+          <t>58,58%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>73,18%</t>
+          <t>73,09%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3860,12 +3860,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>73964</t>
+          <t>72312</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>96430</t>
+          <t>96328</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3875,12 +3875,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>50,53%</t>
+          <t>49,4%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>65,88%</t>
+          <t>65,81%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>176994</t>
+          <t>175767</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>210387</t>
+          <t>209125</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3910,12 +3910,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>56,82%</t>
+          <t>56,42%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>67,54%</t>
+          <t>67,13%</t>
         </is>
       </c>
     </row>
@@ -4055,12 +4055,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>123988</t>
+          <t>123998</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>161306</t>
+          <t>161728</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4075,7 +4075,7 @@
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>46,36%</t>
+          <t>46,49%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4090,12 +4090,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>123716</t>
+          <t>124127</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>156747</t>
+          <t>156896</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4105,12 +4105,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>49,78%</t>
+          <t>49,94%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>63,07%</t>
+          <t>63,13%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4125,12 +4125,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>259703</t>
+          <t>254934</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>308530</t>
+          <t>306029</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4140,12 +4140,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>43,54%</t>
+          <t>42,74%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>51,73%</t>
+          <t>51,31%</t>
         </is>
       </c>
     </row>
@@ -4168,12 +4168,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>186607</t>
+          <t>186185</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>223925</t>
+          <t>223915</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4183,7 +4183,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>53,64%</t>
+          <t>53,51%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
@@ -4203,12 +4203,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>91787</t>
+          <t>91638</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>124818</t>
+          <t>124407</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4218,12 +4218,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>36,93%</t>
+          <t>36,87%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>50,22%</t>
+          <t>50,06%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4238,12 +4238,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>287917</t>
+          <t>290418</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>336744</t>
+          <t>341513</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4253,12 +4253,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>48,27%</t>
+          <t>48,69%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>56,46%</t>
+          <t>57,26%</t>
         </is>
       </c>
     </row>
@@ -4398,12 +4398,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>140439</t>
+          <t>139255</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>176232</t>
+          <t>175959</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4413,12 +4413,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>43,29%</t>
+          <t>42,93%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>54,33%</t>
+          <t>54,25%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4433,12 +4433,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>111431</t>
+          <t>112908</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>143415</t>
+          <t>144306</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4448,12 +4448,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>44,89%</t>
+          <t>45,48%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>57,77%</t>
+          <t>58,13%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4468,12 +4468,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>261967</t>
+          <t>261437</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>309460</t>
+          <t>310738</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4483,12 +4483,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>45,75%</t>
+          <t>45,66%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>54,04%</t>
+          <t>54,27%</t>
         </is>
       </c>
     </row>
@@ -4511,12 +4511,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>148145</t>
+          <t>148418</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>183938</t>
+          <t>185122</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4526,12 +4526,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>45,67%</t>
+          <t>45,75%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>56,71%</t>
+          <t>57,07%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4546,12 +4546,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>104824</t>
+          <t>103933</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>136808</t>
+          <t>135331</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4561,12 +4561,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>42,23%</t>
+          <t>41,87%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>55,11%</t>
+          <t>54,52%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4581,12 +4581,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>263156</t>
+          <t>261878</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>310649</t>
+          <t>311179</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4596,12 +4596,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>45,96%</t>
+          <t>45,73%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>54,25%</t>
+          <t>54,34%</t>
         </is>
       </c>
     </row>
@@ -4741,12 +4741,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>126099</t>
+          <t>129671</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>162504</t>
+          <t>165374</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4756,12 +4756,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>45,07%</t>
+          <t>46,35%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>58,08%</t>
+          <t>59,11%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4776,12 +4776,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>114381</t>
+          <t>114328</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>147539</t>
+          <t>147842</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4791,12 +4791,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>48,24%</t>
+          <t>48,22%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>62,23%</t>
+          <t>62,36%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4811,12 +4811,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>252854</t>
+          <t>253966</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>301045</t>
+          <t>302928</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4826,12 +4826,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>48,92%</t>
+          <t>49,13%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>58,24%</t>
+          <t>58,61%</t>
         </is>
       </c>
     </row>
@@ -4854,12 +4854,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>117278</t>
+          <t>114408</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>153683</t>
+          <t>150111</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4869,12 +4869,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>41,92%</t>
+          <t>40,89%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>54,93%</t>
+          <t>53,65%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4889,12 +4889,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>89554</t>
+          <t>89251</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>122712</t>
+          <t>122765</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4904,12 +4904,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>37,77%</t>
+          <t>37,64%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>51,76%</t>
+          <t>51,78%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4924,12 +4924,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>215830</t>
+          <t>213947</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>264021</t>
+          <t>262909</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4939,12 +4939,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>41,76%</t>
+          <t>41,39%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>51,08%</t>
+          <t>50,87%</t>
         </is>
       </c>
     </row>
@@ -5084,12 +5084,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>73938</t>
+          <t>72619</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>99627</t>
+          <t>98514</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5099,12 +5099,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>47,28%</t>
+          <t>46,44%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>63,71%</t>
+          <t>63,0%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5119,12 +5119,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>18016</t>
+          <t>18212</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>35090</t>
+          <t>35541</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5134,12 +5134,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>27,33%</t>
+          <t>27,63%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>53,23%</t>
+          <t>53,92%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5154,12 +5154,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>96753</t>
+          <t>96583</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>128099</t>
+          <t>128190</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5169,12 +5169,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>43,53%</t>
+          <t>43,45%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>57,63%</t>
+          <t>57,67%</t>
         </is>
       </c>
     </row>
@@ -5197,12 +5197,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>56742</t>
+          <t>57855</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>82431</t>
+          <t>83750</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5212,12 +5212,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>36,29%</t>
+          <t>37,0%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>52,72%</t>
+          <t>53,56%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5232,12 +5232,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>30830</t>
+          <t>30379</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>47904</t>
+          <t>47708</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5247,12 +5247,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>46,77%</t>
+          <t>46,08%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>72,67%</t>
+          <t>72,37%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5267,12 +5267,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>94190</t>
+          <t>94099</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>125536</t>
+          <t>125706</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5282,12 +5282,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>42,37%</t>
+          <t>42,33%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>56,47%</t>
+          <t>56,55%</t>
         </is>
       </c>
     </row>
@@ -5427,12 +5427,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>17559</t>
+          <t>17360</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>33028</t>
+          <t>32409</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5442,12 +5442,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>34,26%</t>
+          <t>33,87%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>64,44%</t>
+          <t>63,23%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5462,12 +5462,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>2925</t>
+          <t>3490</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>12175</t>
+          <t>12369</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5477,12 +5477,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>15,39%</t>
+          <t>18,37%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>64,07%</t>
+          <t>65,09%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5497,12 +5497,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>24029</t>
+          <t>23081</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>41931</t>
+          <t>41132</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5512,12 +5512,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>34,2%</t>
+          <t>32,85%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>59,68%</t>
+          <t>58,54%</t>
         </is>
       </c>
     </row>
@@ -5540,12 +5540,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>18226</t>
+          <t>18845</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>33695</t>
+          <t>33894</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5555,12 +5555,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>35,56%</t>
+          <t>36,77%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>65,74%</t>
+          <t>66,13%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5575,12 +5575,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>6828</t>
+          <t>6634</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>16078</t>
+          <t>15513</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5590,12 +5590,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>35,93%</t>
+          <t>34,91%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>84,61%</t>
+          <t>81,63%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5610,12 +5610,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>28326</t>
+          <t>29125</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>46228</t>
+          <t>47176</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5625,12 +5625,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>40,32%</t>
+          <t>41,46%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>65,8%</t>
+          <t>67,15%</t>
         </is>
       </c>
     </row>
@@ -5770,12 +5770,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>7388</t>
+          <t>7935</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>18487</t>
+          <t>19202</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5785,12 +5785,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>27,31%</t>
+          <t>29,33%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>68,34%</t>
+          <t>70,98%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5840,12 +5840,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>8687</t>
+          <t>8246</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>20497</t>
+          <t>20116</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5855,12 +5855,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>27,95%</t>
+          <t>26,53%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>65,95%</t>
+          <t>64,72%</t>
         </is>
       </c>
     </row>
@@ -5883,12 +5883,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>8565</t>
+          <t>7850</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>19664</t>
+          <t>19117</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5898,12 +5898,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>31,66%</t>
+          <t>29,02%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>72,69%</t>
+          <t>70,67%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5953,12 +5953,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>10583</t>
+          <t>10964</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>22393</t>
+          <t>22834</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5968,12 +5968,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>34,05%</t>
+          <t>35,28%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>72,05%</t>
+          <t>73,47%</t>
         </is>
       </c>
     </row>
@@ -6113,12 +6113,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>588595</t>
+          <t>587726</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>664147</t>
+          <t>662984</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6128,12 +6128,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>43,54%</t>
+          <t>43,47%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>49,13%</t>
+          <t>49,04%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6148,12 +6148,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>463910</t>
+          <t>461690</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>527689</t>
+          <t>528034</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6163,12 +6163,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>47,87%</t>
+          <t>47,64%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>54,45%</t>
+          <t>54,48%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6183,12 +6183,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>1075336</t>
+          <t>1067264</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>1178002</t>
+          <t>1169235</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6198,12 +6198,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>46,33%</t>
+          <t>45,98%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>50,75%</t>
+          <t>50,37%</t>
         </is>
       </c>
     </row>
@@ -6226,12 +6226,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>687745</t>
+          <t>688908</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>763297</t>
+          <t>764166</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6241,12 +6241,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>50,87%</t>
+          <t>50,96%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>56,46%</t>
+          <t>56,53%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6261,12 +6261,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>441505</t>
+          <t>441160</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>505284</t>
+          <t>507504</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6276,12 +6276,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>45,55%</t>
+          <t>45,52%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>52,13%</t>
+          <t>52,36%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6296,12 +6296,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1143084</t>
+          <t>1151851</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1245750</t>
+          <t>1253822</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6311,12 +6311,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>49,25%</t>
+          <t>49,63%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>53,67%</t>
+          <t>54,02%</t>
         </is>
       </c>
     </row>
@@ -6691,12 +6691,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>28861</t>
+          <t>28191</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>51496</t>
+          <t>51433</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6706,12 +6706,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>20,28%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>36,19%</t>
+          <t>36,14%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6726,12 +6726,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>25960</t>
+          <t>26786</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>44785</t>
+          <t>45660</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6741,12 +6741,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>24,62%</t>
+          <t>25,4%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>42,47%</t>
+          <t>43,3%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6761,12 +6761,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>61079</t>
+          <t>60744</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>88851</t>
+          <t>87806</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6776,12 +6776,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>24,65%</t>
+          <t>24,52%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>35,86%</t>
+          <t>35,44%</t>
         </is>
       </c>
     </row>
@@ -6804,12 +6804,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>90806</t>
+          <t>90869</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>113441</t>
+          <t>114111</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6819,12 +6819,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>63,81%</t>
+          <t>63,86%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>79,72%</t>
+          <t>80,19%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6839,12 +6839,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>60662</t>
+          <t>59787</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>79487</t>
+          <t>78661</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6854,12 +6854,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>57,53%</t>
+          <t>56,7%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>75,38%</t>
+          <t>74,6%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6874,12 +6874,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>158897</t>
+          <t>159942</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>186669</t>
+          <t>187004</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6889,12 +6889,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>64,14%</t>
+          <t>64,56%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>75,35%</t>
+          <t>75,48%</t>
         </is>
       </c>
     </row>
@@ -7034,12 +7034,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>83364</t>
+          <t>83214</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>116309</t>
+          <t>114013</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7049,12 +7049,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>31,93%</t>
+          <t>31,87%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>44,55%</t>
+          <t>43,67%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7069,12 +7069,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>74202</t>
+          <t>74862</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>102118</t>
+          <t>102713</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7084,12 +7084,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>34,83%</t>
+          <t>35,14%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>47,94%</t>
+          <t>48,21%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7104,12 +7104,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>167494</t>
+          <t>163724</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>208490</t>
+          <t>207062</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7119,12 +7119,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>35,33%</t>
+          <t>34,53%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>43,97%</t>
+          <t>43,67%</t>
         </is>
       </c>
     </row>
@@ -7147,12 +7147,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>144773</t>
+          <t>147069</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>177718</t>
+          <t>177868</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7162,12 +7162,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>55,45%</t>
+          <t>56,33%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>68,07%</t>
+          <t>68,13%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7182,12 +7182,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>110913</t>
+          <t>110318</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>138829</t>
+          <t>138169</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7197,12 +7197,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>52,06%</t>
+          <t>51,79%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>65,17%</t>
+          <t>64,86%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7217,12 +7217,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>265623</t>
+          <t>267051</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>306619</t>
+          <t>310389</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7232,12 +7232,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>56,03%</t>
+          <t>56,33%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>64,67%</t>
+          <t>65,47%</t>
         </is>
       </c>
     </row>
@@ -7377,12 +7377,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>107977</t>
+          <t>111271</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>141533</t>
+          <t>143818</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7392,12 +7392,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>40,59%</t>
+          <t>41,83%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>53,2%</t>
+          <t>54,06%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7412,12 +7412,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>78804</t>
+          <t>79058</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>105153</t>
+          <t>106235</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7427,12 +7427,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>35,73%</t>
+          <t>35,85%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>47,68%</t>
+          <t>48,17%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7447,12 +7447,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>197260</t>
+          <t>194122</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>239961</t>
+          <t>240618</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7462,12 +7462,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>40,54%</t>
+          <t>39,9%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>49,32%</t>
+          <t>49,45%</t>
         </is>
       </c>
     </row>
@@ -7490,12 +7490,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>124490</t>
+          <t>122205</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>158046</t>
+          <t>154752</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7505,12 +7505,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>46,8%</t>
+          <t>45,94%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>59,41%</t>
+          <t>58,17%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7525,12 +7525,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>115391</t>
+          <t>114309</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>141740</t>
+          <t>141486</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7540,12 +7540,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>52,32%</t>
+          <t>51,83%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>64,27%</t>
+          <t>64,15%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7560,12 +7560,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>246606</t>
+          <t>245949</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>289307</t>
+          <t>292445</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7575,12 +7575,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>50,68%</t>
+          <t>50,55%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>59,46%</t>
+          <t>60,1%</t>
         </is>
       </c>
     </row>
@@ -7720,12 +7720,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>101005</t>
+          <t>102078</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>134608</t>
+          <t>137085</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7735,12 +7735,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>36,36%</t>
+          <t>36,75%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>48,46%</t>
+          <t>49,35%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7755,12 +7755,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>101310</t>
+          <t>103166</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>133309</t>
+          <t>132931</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7770,12 +7770,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>43,89%</t>
+          <t>44,69%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>57,75%</t>
+          <t>57,59%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7790,12 +7790,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>214687</t>
+          <t>212732</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>260641</t>
+          <t>260137</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7805,12 +7805,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>42,21%</t>
+          <t>41,82%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>51,24%</t>
+          <t>51,14%</t>
         </is>
       </c>
     </row>
@@ -7833,12 +7833,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>143190</t>
+          <t>140713</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>176793</t>
+          <t>175720</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7848,12 +7848,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>51,54%</t>
+          <t>50,65%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>63,64%</t>
+          <t>63,25%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7868,12 +7868,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>97520</t>
+          <t>97898</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>129519</t>
+          <t>127663</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7883,12 +7883,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>42,25%</t>
+          <t>42,41%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>56,11%</t>
+          <t>55,31%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7903,12 +7903,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>247986</t>
+          <t>248490</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>293940</t>
+          <t>295895</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7918,12 +7918,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>48,76%</t>
+          <t>48,86%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>57,79%</t>
+          <t>58,18%</t>
         </is>
       </c>
     </row>
@@ -8063,12 +8063,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>68454</t>
+          <t>68736</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>92859</t>
+          <t>92854</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8078,7 +8078,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>46,62%</t>
+          <t>46,81%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
@@ -8098,12 +8098,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>44490</t>
+          <t>45137</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>68460</t>
+          <t>68123</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8113,12 +8113,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>39,0%</t>
+          <t>39,56%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>60,01%</t>
+          <t>59,71%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>121414</t>
+          <t>121699</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>155337</t>
+          <t>156005</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8148,12 +8148,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>46,53%</t>
+          <t>46,64%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>59,53%</t>
+          <t>59,79%</t>
         </is>
       </c>
     </row>
@@ -8176,12 +8176,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>53977</t>
+          <t>53982</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>78382</t>
+          <t>78100</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8196,7 +8196,7 @@
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>53,38%</t>
+          <t>53,19%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8211,12 +8211,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>45627</t>
+          <t>45964</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>69597</t>
+          <t>68950</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8226,12 +8226,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>39,99%</t>
+          <t>40,29%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>61,0%</t>
+          <t>60,44%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8246,12 +8246,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>105587</t>
+          <t>104919</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>139510</t>
+          <t>139225</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8261,12 +8261,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>40,47%</t>
+          <t>40,21%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>53,47%</t>
+          <t>53,36%</t>
         </is>
       </c>
     </row>
@@ -8406,12 +8406,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>21434</t>
+          <t>21109</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>36775</t>
+          <t>36241</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8421,12 +8421,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>36,81%</t>
+          <t>36,25%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>63,15%</t>
+          <t>62,24%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8441,12 +8441,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>8626</t>
+          <t>8170</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>19991</t>
+          <t>20173</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8456,12 +8456,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>28,73%</t>
+          <t>27,21%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>66,58%</t>
+          <t>67,18%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8476,12 +8476,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>33743</t>
+          <t>33504</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>52984</t>
+          <t>52284</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8491,12 +8491,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>38,23%</t>
+          <t>37,96%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>60,03%</t>
+          <t>59,24%</t>
         </is>
       </c>
     </row>
@@ -8519,12 +8519,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>21457</t>
+          <t>21991</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>36798</t>
+          <t>37123</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>36,85%</t>
+          <t>37,76%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>63,19%</t>
+          <t>63,75%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8554,12 +8554,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>10036</t>
+          <t>9854</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>21401</t>
+          <t>21857</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8569,12 +8569,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>33,42%</t>
+          <t>32,82%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>71,27%</t>
+          <t>72,79%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>35275</t>
+          <t>35975</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>54516</t>
+          <t>54755</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8604,12 +8604,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>39,97%</t>
+          <t>40,76%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>61,77%</t>
+          <t>62,04%</t>
         </is>
       </c>
     </row>
@@ -8749,12 +8749,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>8188</t>
+          <t>8399</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>16558</t>
+          <t>17279</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8764,12 +8764,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>34,31%</t>
+          <t>35,2%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>69,39%</t>
+          <t>72,41%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8784,7 +8784,7 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>2790</t>
+          <t>1486</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
@@ -8799,7 +8799,7 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>34,81%</t>
+          <t>18,55%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
@@ -8819,12 +8819,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>12544</t>
+          <t>12079</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>23628</t>
+          <t>22863</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8834,12 +8834,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>39,35%</t>
+          <t>37,89%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>74,12%</t>
+          <t>71,72%</t>
         </is>
       </c>
     </row>
@@ -8862,12 +8862,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>7305</t>
+          <t>6584</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>15675</t>
+          <t>15464</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8877,12 +8877,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>30,61%</t>
+          <t>27,59%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>65,69%</t>
+          <t>64,8%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8902,7 +8902,7 @@
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>5224</t>
+          <t>6528</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8917,7 +8917,7 @@
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>65,19%</t>
+          <t>81,45%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8932,12 +8932,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>8249</t>
+          <t>9014</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>19333</t>
+          <t>19798</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8947,12 +8947,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>25,88%</t>
+          <t>28,28%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>60,65%</t>
+          <t>62,11%</t>
         </is>
       </c>
     </row>
@@ -9092,12 +9092,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>470680</t>
+          <t>470649</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>539975</t>
+          <t>540294</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9112,7 +9112,7 @@
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>45,91%</t>
+          <t>45,94%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9127,12 +9127,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>379914</t>
+          <t>381797</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>442177</t>
+          <t>441009</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9142,12 +9142,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>41,21%</t>
+          <t>41,41%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>47,96%</t>
+          <t>47,83%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9162,12 +9162,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>868049</t>
+          <t>870043</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>964351</t>
+          <t>961813</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9177,12 +9177,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>41,37%</t>
+          <t>41,47%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>45,96%</t>
+          <t>45,84%</t>
         </is>
       </c>
     </row>
@@ -9205,12 +9205,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>636162</t>
+          <t>635843</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>705457</t>
+          <t>705488</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9220,7 +9220,7 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>54,09%</t>
+          <t>54,06%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
@@ -9240,12 +9240,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>479802</t>
+          <t>480970</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>542065</t>
+          <t>540182</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9255,12 +9255,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>52,04%</t>
+          <t>52,17%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>58,79%</t>
+          <t>58,59%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9275,12 +9275,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1133765</t>
+          <t>1136303</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1230067</t>
+          <t>1228073</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9290,12 +9290,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>54,04%</t>
+          <t>54,16%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>58,63%</t>
+          <t>58,53%</t>
         </is>
       </c>
     </row>
@@ -9665,32 +9665,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>14393</t>
+          <t>20851</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>5008</t>
+          <t>9435</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>27706</t>
+          <t>36977</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>16,45%</t>
+          <t>23,27%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>5,72%</t>
+          <t>10,53%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>31,66%</t>
+          <t>41,26%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -9700,32 +9700,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>15464</t>
+          <t>19235</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>7705</t>
+          <t>9463</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>26918</t>
+          <t>30791</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>25,07%</t>
+          <t>28,04%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,49%</t>
+          <t>13,79%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>43,65%</t>
+          <t>44,88%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -9735,32 +9735,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>29857</t>
+          <t>40086</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>16628</t>
+          <t>23209</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>47298</t>
+          <t>57583</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>20,01%</t>
+          <t>25,34%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,15%</t>
+          <t>14,67%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>31,7%</t>
+          <t>36,39%</t>
         </is>
       </c>
     </row>
@@ -9778,32 +9778,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>73116</t>
+          <t>68766</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>59803</t>
+          <t>52640</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>82501</t>
+          <t>80182</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>83,55%</t>
+          <t>76,73%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>68,34%</t>
+          <t>58,74%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>94,28%</t>
+          <t>89,47%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -9813,32 +9813,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>46210</t>
+          <t>49366</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>34756</t>
+          <t>37810</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>53969</t>
+          <t>59138</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>74,93%</t>
+          <t>71,96%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>56,35%</t>
+          <t>55,12%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>87,51%</t>
+          <t>86,21%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -9848,32 +9848,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>119326</t>
+          <t>118132</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>101885</t>
+          <t>100635</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>132555</t>
+          <t>135009</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>79,99%</t>
+          <t>74,66%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>68,3%</t>
+          <t>63,61%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,85%</t>
+          <t>85,33%</t>
         </is>
       </c>
     </row>
@@ -9891,17 +9891,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>87509</t>
+          <t>89617</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>87509</t>
+          <t>89617</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>87509</t>
+          <t>89617</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -9926,17 +9926,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>61674</t>
+          <t>68601</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>61674</t>
+          <t>68601</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>61674</t>
+          <t>68601</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -9961,17 +9961,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>149183</t>
+          <t>158218</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>149183</t>
+          <t>158218</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>149183</t>
+          <t>158218</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -10008,32 +10008,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>35282</t>
+          <t>39902</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>23998</t>
+          <t>26776</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>50222</t>
+          <t>55851</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>24,0%</t>
+          <t>24,69%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,32%</t>
+          <t>16,57%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>34,16%</t>
+          <t>34,56%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -10043,32 +10043,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>42339</t>
+          <t>43064</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>32490</t>
+          <t>32973</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>53428</t>
+          <t>54394</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>37,22%</t>
+          <t>35,61%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>28,56%</t>
+          <t>27,27%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>46,97%</t>
+          <t>44,98%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -10078,32 +10078,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>77621</t>
+          <t>82967</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>60285</t>
+          <t>65006</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>95043</t>
+          <t>100607</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>29,77%</t>
+          <t>29,36%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>23,12%</t>
+          <t>23,01%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>36,45%</t>
+          <t>35,61%</t>
         </is>
       </c>
     </row>
@@ -10121,32 +10121,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>111747</t>
+          <t>121715</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>96807</t>
+          <t>105766</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>123031</t>
+          <t>134841</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>76,0%</t>
+          <t>75,31%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>65,84%</t>
+          <t>65,44%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>83,68%</t>
+          <t>83,43%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -10156,32 +10156,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>71410</t>
+          <t>77859</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>60321</t>
+          <t>66529</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>81259</t>
+          <t>87950</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>62,78%</t>
+          <t>64,39%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>53,03%</t>
+          <t>55,02%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>71,44%</t>
+          <t>72,73%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -10191,32 +10191,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>183156</t>
+          <t>199573</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>165734</t>
+          <t>181933</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>200492</t>
+          <t>217534</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>70,23%</t>
+          <t>70,64%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>63,55%</t>
+          <t>64,39%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>76,88%</t>
+          <t>76,99%</t>
         </is>
       </c>
     </row>
@@ -10234,17 +10234,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>147029</t>
+          <t>161617</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>147029</t>
+          <t>161617</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>147029</t>
+          <t>161617</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -10269,17 +10269,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>113749</t>
+          <t>120923</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>113749</t>
+          <t>120923</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>113749</t>
+          <t>120923</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -10304,17 +10304,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>260777</t>
+          <t>282540</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>260777</t>
+          <t>282540</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>260777</t>
+          <t>282540</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -10351,32 +10351,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>53292</t>
+          <t>62257</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>40889</t>
+          <t>48421</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>65878</t>
+          <t>75234</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>35,61%</t>
+          <t>36,98%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>27,32%</t>
+          <t>28,76%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>44,02%</t>
+          <t>44,69%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -10386,32 +10386,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>61700</t>
+          <t>66708</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>52389</t>
+          <t>56417</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>71636</t>
+          <t>77518</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>45,73%</t>
+          <t>45,87%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>38,83%</t>
+          <t>38,79%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>53,09%</t>
+          <t>53,3%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -10421,32 +10421,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>114993</t>
+          <t>128966</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>99392</t>
+          <t>112358</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>129385</t>
+          <t>145072</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>40,41%</t>
+          <t>41,1%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>34,93%</t>
+          <t>35,81%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>45,47%</t>
+          <t>46,23%</t>
         </is>
       </c>
     </row>
@@ -10464,32 +10464,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>96355</t>
+          <t>106091</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>83769</t>
+          <t>93114</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>108758</t>
+          <t>119927</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>64,39%</t>
+          <t>63,02%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>55,98%</t>
+          <t>55,31%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>72,68%</t>
+          <t>71,24%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -10499,32 +10499,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>73222</t>
+          <t>78719</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>63286</t>
+          <t>67909</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>82533</t>
+          <t>89010</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>54,27%</t>
+          <t>54,13%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>46,91%</t>
+          <t>46,7%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>61,17%</t>
+          <t>61,21%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -10534,32 +10534,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>169576</t>
+          <t>184810</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>155184</t>
+          <t>168704</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>185177</t>
+          <t>201418</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>59,59%</t>
+          <t>58,9%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>54,53%</t>
+          <t>53,77%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>65,07%</t>
+          <t>64,19%</t>
         </is>
       </c>
     </row>
@@ -10577,17 +10577,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>149647</t>
+          <t>168348</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>149647</t>
+          <t>168348</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>149647</t>
+          <t>168348</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -10612,17 +10612,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>134922</t>
+          <t>145427</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>134922</t>
+          <t>145427</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>134922</t>
+          <t>145427</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -10647,17 +10647,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>284569</t>
+          <t>313776</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>284569</t>
+          <t>313776</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>284569</t>
+          <t>313776</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -10694,67 +10694,67 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>77668</t>
+          <t>75557</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>63006</t>
+          <t>62225</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>97496</t>
+          <t>90189</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
+          <t>38,68%</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>31,86%</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>46,17%</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>82673</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>72444</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>93096</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>47,97%</t>
+        </is>
+      </c>
+      <c r="O13" s="2" t="inlineStr">
+        <is>
           <t>42,04%</t>
         </is>
       </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>34,1%</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>52,77%</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>127</t>
-        </is>
-      </c>
-      <c r="K13" s="2" t="inlineStr">
-        <is>
-          <t>77849</t>
-        </is>
-      </c>
-      <c r="L13" s="2" t="inlineStr">
-        <is>
-          <t>68259</t>
-        </is>
-      </c>
-      <c r="M13" s="2" t="inlineStr">
-        <is>
-          <t>86949</t>
-        </is>
-      </c>
-      <c r="N13" s="2" t="inlineStr">
-        <is>
-          <t>48,28%</t>
-        </is>
-      </c>
-      <c r="O13" s="2" t="inlineStr">
-        <is>
-          <t>42,34%</t>
-        </is>
-      </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>53,93%</t>
+          <t>54,02%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -10764,32 +10764,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>155517</t>
+          <t>158230</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>138246</t>
+          <t>139735</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>175241</t>
+          <t>175479</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>44,95%</t>
+          <t>43,04%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>39,96%</t>
+          <t>38,01%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>50,65%</t>
+          <t>47,73%</t>
         </is>
       </c>
     </row>
@@ -10807,69 +10807,69 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>107090</t>
+          <t>119764</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>87262</t>
+          <t>105132</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>121752</t>
+          <t>133096</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
+          <t>61,32%</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>53,83%</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>68,14%</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>89652</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>79229</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>99881</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>52,03%</t>
+        </is>
+      </c>
+      <c r="O14" s="2" t="inlineStr">
+        <is>
+          <t>45,98%</t>
+        </is>
+      </c>
+      <c r="P14" s="2" t="inlineStr">
+        <is>
           <t>57,96%</t>
         </is>
       </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>47,23%</t>
-        </is>
-      </c>
-      <c r="I14" s="2" t="inlineStr">
-        <is>
-          <t>65,9%</t>
-        </is>
-      </c>
-      <c r="J14" s="2" t="inlineStr">
-        <is>
-          <t>145</t>
-        </is>
-      </c>
-      <c r="K14" s="2" t="inlineStr">
-        <is>
-          <t>83385</t>
-        </is>
-      </c>
-      <c r="L14" s="2" t="inlineStr">
-        <is>
-          <t>74285</t>
-        </is>
-      </c>
-      <c r="M14" s="2" t="inlineStr">
-        <is>
-          <t>92975</t>
-        </is>
-      </c>
-      <c r="N14" s="2" t="inlineStr">
-        <is>
-          <t>51,72%</t>
-        </is>
-      </c>
-      <c r="O14" s="2" t="inlineStr">
-        <is>
-          <t>46,07%</t>
-        </is>
-      </c>
-      <c r="P14" s="2" t="inlineStr">
-        <is>
-          <t>57,66%</t>
-        </is>
-      </c>
       <c r="Q14" s="2" t="inlineStr">
         <is>
           <t>260</t>
@@ -10877,32 +10877,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>190475</t>
+          <t>209416</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>170751</t>
+          <t>192167</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>207746</t>
+          <t>227911</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>55,05%</t>
+          <t>56,96%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>49,35%</t>
+          <t>52,27%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>60,04%</t>
+          <t>61,99%</t>
         </is>
       </c>
     </row>
@@ -10920,17 +10920,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>184758</t>
+          <t>195321</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>184758</t>
+          <t>195321</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>184758</t>
+          <t>195321</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -10955,17 +10955,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>161234</t>
+          <t>172325</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>161234</t>
+          <t>172325</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>161234</t>
+          <t>172325</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -10990,17 +10990,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>345992</t>
+          <t>367646</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>345992</t>
+          <t>367646</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>345992</t>
+          <t>367646</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">
@@ -11037,32 +11037,32 @@
       </c>
       <c r="D16" s="2" t="inlineStr">
         <is>
-          <t>71863</t>
+          <t>78328</t>
         </is>
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>59373</t>
+          <t>65810</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>83559</t>
+          <t>91501</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
         <is>
-          <t>41,97%</t>
+          <t>42,28%</t>
         </is>
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>34,67%</t>
+          <t>35,52%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>48,8%</t>
+          <t>49,39%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -11072,32 +11072,32 @@
       </c>
       <c r="K16" s="2" t="inlineStr">
         <is>
-          <t>60517</t>
+          <t>68736</t>
         </is>
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>52795</t>
+          <t>59700</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>68860</t>
+          <t>78031</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>50,54%</t>
+          <t>51,94%</t>
         </is>
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>44,09%</t>
+          <t>45,12%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>57,5%</t>
+          <t>58,97%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -11107,32 +11107,32 @@
       </c>
       <c r="R16" s="2" t="inlineStr">
         <is>
-          <t>132381</t>
+          <t>147065</t>
         </is>
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>116950</t>
+          <t>132233</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>146997</t>
+          <t>162514</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
         <is>
-          <t>45,49%</t>
+          <t>46,3%</t>
         </is>
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>40,19%</t>
+          <t>41,63%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>50,52%</t>
+          <t>51,17%</t>
         </is>
       </c>
     </row>
@@ -11150,32 +11150,32 @@
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>99376</t>
+          <t>106951</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>87680</t>
+          <t>93778</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>111866</t>
+          <t>119469</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>58,03%</t>
+          <t>57,72%</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>51,2%</t>
+          <t>50,61%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>65,33%</t>
+          <t>64,48%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -11185,32 +11185,32 @@
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>59236</t>
+          <t>63592</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>50893</t>
+          <t>54297</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>66958</t>
+          <t>72628</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>49,46%</t>
+          <t>48,06%</t>
         </is>
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>42,5%</t>
+          <t>41,03%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>55,91%</t>
+          <t>54,88%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -11220,32 +11220,32 @@
       </c>
       <c r="R17" s="2" t="inlineStr">
         <is>
-          <t>158611</t>
+          <t>170543</t>
         </is>
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>143995</t>
+          <t>155094</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>174042</t>
+          <t>185375</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
         <is>
-          <t>54,51%</t>
+          <t>53,7%</t>
         </is>
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>49,48%</t>
+          <t>48,83%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>59,81%</t>
+          <t>58,37%</t>
         </is>
       </c>
     </row>
@@ -11263,17 +11263,17 @@
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>171239</t>
+          <t>185279</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>171239</t>
+          <t>185279</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>171239</t>
+          <t>185279</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -11298,17 +11298,17 @@
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>119753</t>
+          <t>132328</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>119753</t>
+          <t>132328</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>119753</t>
+          <t>132328</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
@@ -11333,17 +11333,17 @@
       </c>
       <c r="R18" s="2" t="inlineStr">
         <is>
-          <t>290992</t>
+          <t>317608</t>
         </is>
       </c>
       <c r="S18" s="2" t="inlineStr">
         <is>
-          <t>290992</t>
+          <t>317608</t>
         </is>
       </c>
       <c r="T18" s="2" t="inlineStr">
         <is>
-          <t>290992</t>
+          <t>317608</t>
         </is>
       </c>
       <c r="U18" s="2" t="inlineStr">
@@ -11380,32 +11380,32 @@
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>32925</t>
+          <t>36567</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>26353</t>
+          <t>29367</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>39849</t>
+          <t>43933</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>48,71%</t>
+          <t>49,43%</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>38,99%</t>
+          <t>39,69%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>58,95%</t>
+          <t>59,38%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -11415,32 +11415,32 @@
       </c>
       <c r="K19" s="2" t="inlineStr">
         <is>
-          <t>21627</t>
+          <t>24216</t>
         </is>
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>16565</t>
+          <t>18615</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>26960</t>
+          <t>29685</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
         <is>
-          <t>44,34%</t>
+          <t>44,38%</t>
         </is>
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>33,96%</t>
+          <t>34,12%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>55,27%</t>
+          <t>54,41%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -11450,32 +11450,32 @@
       </c>
       <c r="R19" s="2" t="inlineStr">
         <is>
-          <t>54552</t>
+          <t>60782</t>
         </is>
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>46389</t>
+          <t>51910</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>63151</t>
+          <t>70089</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
         <is>
-          <t>46,88%</t>
+          <t>47,28%</t>
         </is>
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>39,86%</t>
+          <t>40,38%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>54,27%</t>
+          <t>54,52%</t>
         </is>
       </c>
     </row>
@@ -11493,32 +11493,32 @@
       </c>
       <c r="D20" s="2" t="inlineStr">
         <is>
-          <t>34670</t>
+          <t>37416</t>
         </is>
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>27746</t>
+          <t>30050</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>41242</t>
+          <t>44616</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
         <is>
-          <t>51,29%</t>
+          <t>50,57%</t>
         </is>
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>41,05%</t>
+          <t>40,62%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>61,01%</t>
+          <t>60,31%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -11528,32 +11528,32 @@
       </c>
       <c r="K20" s="2" t="inlineStr">
         <is>
-          <t>27153</t>
+          <t>30347</t>
         </is>
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>21820</t>
+          <t>24878</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>32215</t>
+          <t>35948</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>55,66%</t>
+          <t>55,62%</t>
         </is>
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>44,73%</t>
+          <t>45,59%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>66,04%</t>
+          <t>65,88%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -11563,32 +11563,32 @@
       </c>
       <c r="R20" s="2" t="inlineStr">
         <is>
-          <t>61822</t>
+          <t>67764</t>
         </is>
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>53223</t>
+          <t>58457</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>69985</t>
+          <t>76636</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
         <is>
-          <t>53,12%</t>
+          <t>52,72%</t>
         </is>
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>45,73%</t>
+          <t>45,48%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>60,14%</t>
+          <t>59,62%</t>
         </is>
       </c>
     </row>
@@ -11606,17 +11606,17 @@
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>67595</t>
+          <t>73983</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>67595</t>
+          <t>73983</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>67595</t>
+          <t>73983</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
@@ -11641,17 +11641,17 @@
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>48780</t>
+          <t>54563</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>48780</t>
+          <t>54563</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>48780</t>
+          <t>54563</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
@@ -11676,17 +11676,17 @@
       </c>
       <c r="R21" s="2" t="inlineStr">
         <is>
-          <t>116374</t>
+          <t>128546</t>
         </is>
       </c>
       <c r="S21" s="2" t="inlineStr">
         <is>
-          <t>116374</t>
+          <t>128546</t>
         </is>
       </c>
       <c r="T21" s="2" t="inlineStr">
         <is>
-          <t>116374</t>
+          <t>128546</t>
         </is>
       </c>
       <c r="U21" s="2" t="inlineStr">
@@ -11723,32 +11723,32 @@
       </c>
       <c r="D22" s="2" t="inlineStr">
         <is>
-          <t>5870</t>
+          <t>6369</t>
         </is>
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>3063</t>
+          <t>3598</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>9495</t>
+          <t>10286</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
         <is>
-          <t>30,85%</t>
+          <t>31,54%</t>
         </is>
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>17,82%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>49,89%</t>
+          <t>50,93%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -11758,32 +11758,32 @@
       </c>
       <c r="K22" s="2" t="inlineStr">
         <is>
-          <t>2213</t>
+          <t>2399</t>
         </is>
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>585</t>
+          <t>631</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>4139</t>
+          <t>4478</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
         <is>
-          <t>35,16%</t>
+          <t>35,4%</t>
         </is>
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>9,3%</t>
+          <t>9,31%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>65,76%</t>
+          <t>66,06%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -11793,32 +11793,32 @@
       </c>
       <c r="R22" s="2" t="inlineStr">
         <is>
-          <t>8083</t>
+          <t>8768</t>
         </is>
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>5141</t>
+          <t>4979</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>11924</t>
+          <t>12751</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
         <is>
-          <t>31,92%</t>
+          <t>32,51%</t>
         </is>
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>20,3%</t>
+          <t>18,46%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>47,09%</t>
+          <t>47,28%</t>
         </is>
       </c>
     </row>
@@ -11836,32 +11836,32 @@
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>13161</t>
+          <t>13826</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>9536</t>
+          <t>9909</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>15968</t>
+          <t>16597</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>69,15%</t>
+          <t>68,46%</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>50,11%</t>
+          <t>49,07%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>83,91%</t>
+          <t>82,18%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -11871,32 +11871,32 @@
       </c>
       <c r="K23" s="2" t="inlineStr">
         <is>
-          <t>4081</t>
+          <t>4379</t>
         </is>
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>2155</t>
+          <t>2300</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>5709</t>
+          <t>6147</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>64,84%</t>
+          <t>64,6%</t>
         </is>
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>34,24%</t>
+          <t>33,94%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>90,7%</t>
+          <t>90,69%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -11906,32 +11906,32 @@
       </c>
       <c r="R23" s="2" t="inlineStr">
         <is>
-          <t>17242</t>
+          <t>18204</t>
         </is>
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>13401</t>
+          <t>14221</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>20184</t>
+          <t>21993</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
         <is>
-          <t>68,08%</t>
+          <t>67,49%</t>
         </is>
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>52,91%</t>
+          <t>52,72%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>79,7%</t>
+          <t>81,54%</t>
         </is>
       </c>
     </row>
@@ -11949,17 +11949,17 @@
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>19031</t>
+          <t>20195</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>19031</t>
+          <t>20195</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>19031</t>
+          <t>20195</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
@@ -11984,17 +11984,17 @@
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>6294</t>
+          <t>6778</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>6294</t>
+          <t>6778</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>6294</t>
+          <t>6778</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
@@ -12019,17 +12019,17 @@
       </c>
       <c r="R24" s="2" t="inlineStr">
         <is>
-          <t>25325</t>
+          <t>26972</t>
         </is>
       </c>
       <c r="S24" s="2" t="inlineStr">
         <is>
-          <t>25325</t>
+          <t>26972</t>
         </is>
       </c>
       <c r="T24" s="2" t="inlineStr">
         <is>
-          <t>25325</t>
+          <t>26972</t>
         </is>
       </c>
       <c r="U24" s="2" t="inlineStr">
@@ -12066,32 +12066,32 @@
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>291294</t>
+          <t>319831</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>263266</t>
+          <t>285482</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>325930</t>
+          <t>353950</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>35,23%</t>
+          <t>35,76%</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>31,84%</t>
+          <t>31,92%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>39,42%</t>
+          <t>39,58%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -12101,32 +12101,32 @@
       </c>
       <c r="K25" s="2" t="inlineStr">
         <is>
-          <t>281709</t>
+          <t>307031</t>
         </is>
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>259098</t>
+          <t>282477</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>304949</t>
+          <t>329045</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
         <is>
-          <t>43,58%</t>
+          <t>43,8%</t>
         </is>
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>40,08%</t>
+          <t>40,3%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>47,18%</t>
+          <t>46,94%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -12136,32 +12136,32 @@
       </c>
       <c r="R25" s="2" t="inlineStr">
         <is>
-          <t>573003</t>
+          <t>626863</t>
         </is>
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>533230</t>
+          <t>588102</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>613310</t>
+          <t>669762</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
         <is>
-          <t>38,89%</t>
+          <t>39,29%</t>
         </is>
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>36,2%</t>
+          <t>36,86%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>41,63%</t>
+          <t>41,98%</t>
         </is>
       </c>
     </row>
@@ -12179,32 +12179,32 @@
       </c>
       <c r="D26" s="2" t="inlineStr">
         <is>
-          <t>535514</t>
+          <t>574529</t>
         </is>
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>500878</t>
+          <t>540410</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>563542</t>
+          <t>608878</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
         <is>
-          <t>64,77%</t>
+          <t>64,24%</t>
         </is>
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>60,58%</t>
+          <t>60,42%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>68,16%</t>
+          <t>68,08%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -12214,32 +12214,32 @@
       </c>
       <c r="K26" s="2" t="inlineStr">
         <is>
-          <t>364696</t>
+          <t>393914</t>
         </is>
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>341456</t>
+          <t>371900</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>387307</t>
+          <t>418468</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
         <is>
-          <t>56,42%</t>
+          <t>56,2%</t>
         </is>
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>52,82%</t>
+          <t>53,06%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>59,92%</t>
+          <t>59,7%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -12249,32 +12249,32 @@
       </c>
       <c r="R26" s="2" t="inlineStr">
         <is>
-          <t>900209</t>
+          <t>968443</t>
         </is>
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>859902</t>
+          <t>925544</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>939982</t>
+          <t>1007204</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
         <is>
-          <t>61,11%</t>
+          <t>60,71%</t>
         </is>
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>58,37%</t>
+          <t>58,02%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>63,8%</t>
+          <t>63,14%</t>
         </is>
       </c>
     </row>
@@ -12292,17 +12292,17 @@
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>826808</t>
+          <t>894360</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>826808</t>
+          <t>894360</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>826808</t>
+          <t>894360</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
@@ -12327,17 +12327,17 @@
       </c>
       <c r="K27" s="2" t="inlineStr">
         <is>
-          <t>646405</t>
+          <t>700945</t>
         </is>
       </c>
       <c r="L27" s="2" t="inlineStr">
         <is>
-          <t>646405</t>
+          <t>700945</t>
         </is>
       </c>
       <c r="M27" s="2" t="inlineStr">
         <is>
-          <t>646405</t>
+          <t>700945</t>
         </is>
       </c>
       <c r="N27" s="2" t="inlineStr">
@@ -12362,17 +12362,17 @@
       </c>
       <c r="R27" s="2" t="inlineStr">
         <is>
-          <t>1473212</t>
+          <t>1595306</t>
         </is>
       </c>
       <c r="S27" s="2" t="inlineStr">
         <is>
-          <t>1473212</t>
+          <t>1595306</t>
         </is>
       </c>
       <c r="T27" s="2" t="inlineStr">
         <is>
-          <t>1473212</t>
+          <t>1595306</t>
         </is>
       </c>
       <c r="U27" s="2" t="inlineStr">
